--- a/document/ProjectUsing/workDoc/新人工作.xlsx
+++ b/document/ProjectUsing/workDoc/新人工作.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SecretPlace\document\ProjectUsing\workDoc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Work\Project\ProjectOne\document\ProjectUsing\workDoc\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DAE185-543A-4112-BD11-C8FC19A9593D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8868" activeTab="1"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="15196" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="83">
   <si>
     <t>前台</t>
   </si>
@@ -239,33 +240,6 @@
   </si>
   <si>
     <t>列表</t>
-  </si>
-  <si>
-    <r>
-      <t>這個帳號分給甚麼人</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>需要什麼樣的權限</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>統計報表</t>
@@ -316,14 +290,6 @@
   </si>
   <si>
     <t>網頁管理分類下</t>
-  </si>
-  <si>
-    <t>後臺管理分類下</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>最高等級管理員才可以修改帳號等級(?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>可加功能:(查詢)登入日誌、操作日誌</t>
@@ -404,42 +370,11 @@
     </r>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
-  <si>
-    <t>狀態</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>可加功能</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>為了避免異動價格時, 使用者並不清楚, 可以擴增日記內容查詢</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="13">
     <font>
       <sz val="10"/>
@@ -827,17 +762,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:P59"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="16.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.6">
+    <row r="1" spans="1:16" ht="15">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -855,7 +790,7 @@
       <c r="O1" s="5"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="1:16" ht="15.6">
+    <row r="2" spans="1:16" ht="15">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -879,7 +814,7 @@
       </c>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="1:16" ht="15.6">
+    <row r="3" spans="1:16" ht="15">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -917,7 +852,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.6">
+    <row r="4" spans="1:16" ht="15">
       <c r="A4" s="15"/>
       <c r="B4" s="16"/>
       <c r="C4" s="10" t="s">
@@ -943,7 +878,7 @@
       <c r="O4" s="5"/>
       <c r="P4" s="2"/>
     </row>
-    <row r="5" spans="1:16" ht="15.6">
+    <row r="5" spans="1:16" ht="15">
       <c r="A5" s="15"/>
       <c r="B5" s="16"/>
       <c r="C5" s="10" t="s">
@@ -969,7 +904,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="2"/>
     </row>
-    <row r="6" spans="1:16" ht="15.6">
+    <row r="6" spans="1:16" ht="15">
       <c r="A6" s="15"/>
       <c r="B6" s="16"/>
       <c r="C6" s="10" t="s">
@@ -995,7 +930,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="2"/>
     </row>
-    <row r="7" spans="1:16" ht="15.6">
+    <row r="7" spans="1:16" ht="15">
       <c r="A7" s="15"/>
       <c r="B7" s="16"/>
       <c r="C7" s="10" t="s">
@@ -1019,7 +954,7 @@
       <c r="O7" s="5"/>
       <c r="P7" s="2"/>
     </row>
-    <row r="8" spans="1:16" ht="15.6">
+    <row r="8" spans="1:16" ht="15">
       <c r="A8" s="15"/>
       <c r="B8" s="9" t="s">
         <v>20</v>
@@ -1041,7 +976,7 @@
       <c r="O8" s="5"/>
       <c r="P8" s="2"/>
     </row>
-    <row r="9" spans="1:16" ht="15.6">
+    <row r="9" spans="1:16" ht="15">
       <c r="A9" s="15"/>
       <c r="B9" s="9" t="s">
         <v>22</v>
@@ -1063,7 +998,7 @@
       <c r="O9" s="5"/>
       <c r="P9" s="2"/>
     </row>
-    <row r="10" spans="1:16" ht="15.6">
+    <row r="10" spans="1:16" ht="15">
       <c r="A10" s="15"/>
       <c r="B10" s="9" t="s">
         <v>24</v>
@@ -1085,7 +1020,7 @@
       <c r="O10" s="5"/>
       <c r="P10" s="2"/>
     </row>
-    <row r="11" spans="1:16" ht="15.6">
+    <row r="11" spans="1:16" ht="15">
       <c r="A11" s="15"/>
       <c r="B11" s="9" t="s">
         <v>26</v>
@@ -1107,7 +1042,7 @@
       <c r="O11" s="5"/>
       <c r="P11" s="2"/>
     </row>
-    <row r="12" spans="1:16" ht="15.6">
+    <row r="12" spans="1:16" ht="15">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="10" t="s">
@@ -1131,7 +1066,7 @@
       <c r="O12" s="5"/>
       <c r="P12" s="2"/>
     </row>
-    <row r="13" spans="1:16" ht="15.6">
+    <row r="13" spans="1:16" ht="15">
       <c r="A13" s="15"/>
       <c r="B13" s="16"/>
       <c r="C13" s="10" t="s">
@@ -1153,7 +1088,7 @@
       <c r="O13" s="5"/>
       <c r="P13" s="2"/>
     </row>
-    <row r="14" spans="1:16" ht="15.6">
+    <row r="14" spans="1:16" ht="15">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="18"/>
@@ -1173,7 +1108,7 @@
       <c r="O14" s="5"/>
       <c r="P14" s="2"/>
     </row>
-    <row r="15" spans="1:16" ht="15.6">
+    <row r="15" spans="1:16" ht="15">
       <c r="A15" s="8" t="s">
         <v>32</v>
       </c>
@@ -1195,7 +1130,7 @@
       <c r="O15" s="5"/>
       <c r="P15" s="2"/>
     </row>
-    <row r="16" spans="1:16" ht="15.6">
+    <row r="16" spans="1:16" ht="15">
       <c r="A16" s="15"/>
       <c r="B16" s="9" t="s">
         <v>34</v>
@@ -1223,7 +1158,7 @@
       <c r="O16" s="5"/>
       <c r="P16" s="2"/>
     </row>
-    <row r="17" spans="1:16" ht="15.6">
+    <row r="17" spans="1:16" ht="15">
       <c r="A17" s="15"/>
       <c r="B17" s="16"/>
       <c r="C17" s="10" t="s">
@@ -1245,7 +1180,7 @@
       <c r="O17" s="5"/>
       <c r="P17" s="2"/>
     </row>
-    <row r="18" spans="1:16" ht="15.6">
+    <row r="18" spans="1:16" ht="15">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="10" t="s">
@@ -1269,7 +1204,7 @@
       <c r="O18" s="5"/>
       <c r="P18" s="2"/>
     </row>
-    <row r="19" spans="1:16" ht="15.6">
+    <row r="19" spans="1:16" ht="15">
       <c r="A19" s="15"/>
       <c r="B19" s="16"/>
       <c r="C19" s="10" t="s">
@@ -1291,7 +1226,7 @@
       <c r="O19" s="5"/>
       <c r="P19" s="2"/>
     </row>
-    <row r="20" spans="1:16" ht="15.6">
+    <row r="20" spans="1:16" ht="15">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="10" t="s">
@@ -1313,7 +1248,7 @@
       <c r="O20" s="5"/>
       <c r="P20" s="2"/>
     </row>
-    <row r="21" spans="1:16" ht="15.6">
+    <row r="21" spans="1:16" ht="15">
       <c r="A21" s="15"/>
       <c r="B21" s="16"/>
       <c r="C21" s="10" t="s">
@@ -1335,7 +1270,7 @@
       <c r="O21" s="5"/>
       <c r="P21" s="2"/>
     </row>
-    <row r="22" spans="1:16" ht="15.6">
+    <row r="22" spans="1:16" ht="15">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="10" t="s">
@@ -1359,7 +1294,7 @@
       <c r="O22" s="5"/>
       <c r="P22" s="2"/>
     </row>
-    <row r="23" spans="1:16" ht="15.6">
+    <row r="23" spans="1:16" ht="15">
       <c r="A23" s="15"/>
       <c r="B23" s="16"/>
       <c r="C23" s="18"/>
@@ -1379,7 +1314,7 @@
       <c r="O23" s="5"/>
       <c r="P23" s="2"/>
     </row>
-    <row r="24" spans="1:16" ht="15.6">
+    <row r="24" spans="1:16" ht="15">
       <c r="A24" s="15"/>
       <c r="B24" s="9" t="s">
         <v>45</v>
@@ -1403,7 +1338,7 @@
       <c r="O24" s="5"/>
       <c r="P24" s="2"/>
     </row>
-    <row r="25" spans="1:16" ht="15.6">
+    <row r="25" spans="1:16" ht="15">
       <c r="A25" s="15"/>
       <c r="B25" s="16"/>
       <c r="C25" s="10" t="s">
@@ -1429,7 +1364,7 @@
       <c r="O25" s="5"/>
       <c r="P25" s="2"/>
     </row>
-    <row r="26" spans="1:16" ht="15.6">
+    <row r="26" spans="1:16" ht="15">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="10" t="s">
@@ -1451,7 +1386,7 @@
       <c r="O26" s="5"/>
       <c r="P26" s="2"/>
     </row>
-    <row r="27" spans="1:16" ht="15.6">
+    <row r="27" spans="1:16" ht="15">
       <c r="A27" s="15"/>
       <c r="B27" s="16"/>
       <c r="C27" s="10" t="s">
@@ -1471,7 +1406,7 @@
       <c r="O27" s="5"/>
       <c r="P27" s="2"/>
     </row>
-    <row r="28" spans="1:16" ht="15.6">
+    <row r="28" spans="1:16" ht="15">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="10" t="s">
@@ -1491,7 +1426,7 @@
       <c r="O28" s="5"/>
       <c r="P28" s="2"/>
     </row>
-    <row r="29" spans="1:16" ht="15.6">
+    <row r="29" spans="1:16" ht="15">
       <c r="A29" s="15"/>
       <c r="B29" s="16"/>
       <c r="C29" s="10" t="s">
@@ -1511,7 +1446,7 @@
       <c r="O29" s="5"/>
       <c r="P29" s="2"/>
     </row>
-    <row r="30" spans="1:16" ht="15.6">
+    <row r="30" spans="1:16" ht="15">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="10" t="s">
@@ -1549,7 +1484,7 @@
       <c r="O31" s="5"/>
       <c r="P31" s="2"/>
     </row>
-    <row r="32" spans="1:16" ht="15.6">
+    <row r="32" spans="1:16" ht="15">
       <c r="A32" s="8" t="s">
         <v>46</v>
       </c>
@@ -1571,7 +1506,7 @@
       <c r="O32" s="5"/>
       <c r="P32" s="2"/>
     </row>
-    <row r="33" spans="1:16" ht="15.6">
+    <row r="33" spans="1:16" ht="15">
       <c r="A33" s="8"/>
       <c r="B33" s="9" t="s">
         <v>33</v>
@@ -1591,7 +1526,7 @@
       <c r="O33" s="5"/>
       <c r="P33" s="2"/>
     </row>
-    <row r="34" spans="1:16" ht="15.6">
+    <row r="34" spans="1:16" ht="15">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="10"/>
@@ -1609,7 +1544,7 @@
       <c r="O34" s="5"/>
       <c r="P34" s="2"/>
     </row>
-    <row r="35" spans="1:16" ht="15.6">
+    <row r="35" spans="1:16" ht="15">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="10"/>
@@ -1627,7 +1562,7 @@
       <c r="O35" s="5"/>
       <c r="P35" s="2"/>
     </row>
-    <row r="36" spans="1:16" ht="15.6">
+    <row r="36" spans="1:16" ht="15">
       <c r="A36" s="8" t="s">
         <v>48</v>
       </c>
@@ -1661,7 +1596,7 @@
       <c r="O36" s="5"/>
       <c r="P36" s="2"/>
     </row>
-    <row r="37" spans="1:16" ht="15.6">
+    <row r="37" spans="1:16" ht="15">
       <c r="A37" s="15"/>
       <c r="B37" s="16"/>
       <c r="C37" s="10" t="s">
@@ -1683,7 +1618,7 @@
       <c r="O37" s="5"/>
       <c r="P37" s="2"/>
     </row>
-    <row r="38" spans="1:16" ht="15.6">
+    <row r="38" spans="1:16" ht="15">
       <c r="A38" s="15"/>
       <c r="B38" s="16"/>
       <c r="C38" s="10" t="s">
@@ -1705,7 +1640,7 @@
       <c r="O38" s="5"/>
       <c r="P38" s="2"/>
     </row>
-    <row r="39" spans="1:16" ht="15.6">
+    <row r="39" spans="1:16" ht="15">
       <c r="A39" s="15"/>
       <c r="B39" s="16"/>
       <c r="C39" s="10" t="s">
@@ -1729,7 +1664,7 @@
       <c r="O39" s="5"/>
       <c r="P39" s="2"/>
     </row>
-    <row r="40" spans="1:16" ht="15.6">
+    <row r="40" spans="1:16" ht="15">
       <c r="A40" s="15"/>
       <c r="B40" s="16"/>
       <c r="C40" s="10" t="s">
@@ -1751,7 +1686,7 @@
       <c r="O40" s="5"/>
       <c r="P40" s="2"/>
     </row>
-    <row r="41" spans="1:16" ht="15.6">
+    <row r="41" spans="1:16" ht="15">
       <c r="A41" s="15"/>
       <c r="B41" s="16"/>
       <c r="C41" s="10" t="s">
@@ -1773,7 +1708,7 @@
       <c r="O41" s="5"/>
       <c r="P41" s="2"/>
     </row>
-    <row r="42" spans="1:16" ht="15.6">
+    <row r="42" spans="1:16" ht="15">
       <c r="A42" s="15"/>
       <c r="B42" s="16"/>
       <c r="C42" s="10" t="s">
@@ -1795,7 +1730,7 @@
       <c r="O42" s="5"/>
       <c r="P42" s="2"/>
     </row>
-    <row r="43" spans="1:16" ht="15.6">
+    <row r="43" spans="1:16" ht="15">
       <c r="A43" s="15"/>
       <c r="B43" s="16"/>
       <c r="C43" s="10" t="s">
@@ -1817,7 +1752,7 @@
       <c r="O43" s="5"/>
       <c r="P43" s="2"/>
     </row>
-    <row r="44" spans="1:16" ht="15.6">
+    <row r="44" spans="1:16" ht="15">
       <c r="A44" s="15"/>
       <c r="B44" s="16"/>
       <c r="C44" s="18"/>
@@ -1835,7 +1770,7 @@
       <c r="O44" s="5"/>
       <c r="P44" s="2"/>
     </row>
-    <row r="45" spans="1:16" ht="15.6">
+    <row r="45" spans="1:16" ht="15">
       <c r="A45" s="15"/>
       <c r="B45" s="9" t="s">
         <v>60</v>
@@ -1857,7 +1792,7 @@
       <c r="O45" s="5"/>
       <c r="P45" s="2"/>
     </row>
-    <row r="46" spans="1:16" ht="15.6">
+    <row r="46" spans="1:16" ht="15">
       <c r="A46" s="15"/>
       <c r="B46" s="16"/>
       <c r="C46" s="10" t="s">
@@ -1877,7 +1812,7 @@
       <c r="O46" s="5"/>
       <c r="P46" s="2"/>
     </row>
-    <row r="47" spans="1:16" ht="15.6">
+    <row r="47" spans="1:16" ht="15">
       <c r="A47" s="15"/>
       <c r="B47" s="16"/>
       <c r="C47" s="10" t="s">
@@ -1897,7 +1832,7 @@
       <c r="O47" s="5"/>
       <c r="P47" s="2"/>
     </row>
-    <row r="48" spans="1:16" ht="15.6">
+    <row r="48" spans="1:16" ht="15">
       <c r="A48" s="15"/>
       <c r="B48" s="16"/>
       <c r="C48" s="10" t="s">
@@ -1917,7 +1852,7 @@
       <c r="O48" s="5"/>
       <c r="P48" s="2"/>
     </row>
-    <row r="49" spans="1:16" ht="15.6">
+    <row r="49" spans="1:16" ht="15">
       <c r="A49" s="15"/>
       <c r="B49" s="16"/>
       <c r="C49" s="10" t="s">
@@ -1937,7 +1872,7 @@
       <c r="O49" s="5"/>
       <c r="P49" s="2"/>
     </row>
-    <row r="50" spans="1:16" ht="15.6">
+    <row r="50" spans="1:16" ht="15">
       <c r="A50" s="15"/>
       <c r="B50" s="16"/>
       <c r="C50" s="10" t="s">
@@ -1957,7 +1892,7 @@
       <c r="O50" s="5"/>
       <c r="P50" s="2"/>
     </row>
-    <row r="51" spans="1:16" ht="15.6">
+    <row r="51" spans="1:16" ht="15">
       <c r="A51" s="15"/>
       <c r="B51" s="16"/>
       <c r="C51" s="10" t="s">
@@ -1977,7 +1912,7 @@
       <c r="O51" s="5"/>
       <c r="P51" s="2"/>
     </row>
-    <row r="52" spans="1:16" ht="15.6">
+    <row r="52" spans="1:16" ht="15">
       <c r="A52" s="15"/>
       <c r="B52" s="16"/>
       <c r="C52" s="10" t="s">
@@ -2001,7 +1936,7 @@
       <c r="O52" s="5"/>
       <c r="P52" s="2"/>
     </row>
-    <row r="53" spans="1:16" ht="15.6">
+    <row r="53" spans="1:16" ht="15">
       <c r="A53" s="15"/>
       <c r="B53" s="16"/>
       <c r="C53" s="18"/>
@@ -2021,7 +1956,7 @@
       <c r="O53" s="5"/>
       <c r="P53" s="2"/>
     </row>
-    <row r="54" spans="1:16" ht="15.6">
+    <row r="54" spans="1:16" ht="15">
       <c r="A54" s="5"/>
       <c r="B54" s="2"/>
       <c r="C54" s="6"/>
@@ -2041,7 +1976,7 @@
       <c r="O54" s="5"/>
       <c r="P54" s="2"/>
     </row>
-    <row r="55" spans="1:16" ht="15.6">
+    <row r="55" spans="1:16" ht="15">
       <c r="A55" s="5"/>
       <c r="B55" s="2"/>
       <c r="C55" s="6"/>
@@ -2059,7 +1994,7 @@
       <c r="O55" s="5"/>
       <c r="P55" s="2"/>
     </row>
-    <row r="56" spans="1:16" ht="15.6">
+    <row r="56" spans="1:16" ht="15">
       <c r="A56" s="13" t="s">
         <v>64</v>
       </c>
@@ -2081,7 +2016,7 @@
       <c r="O56" s="5"/>
       <c r="P56" s="2"/>
     </row>
-    <row r="57" spans="1:16" ht="15.6">
+    <row r="57" spans="1:16" ht="15">
       <c r="A57" s="5"/>
       <c r="B57" s="14" t="s">
         <v>66</v>
@@ -2101,7 +2036,7 @@
       <c r="O57" s="5"/>
       <c r="P57" s="2"/>
     </row>
-    <row r="58" spans="1:16" ht="15.6">
+    <row r="58" spans="1:16" ht="15">
       <c r="A58" s="5"/>
       <c r="B58" s="2"/>
       <c r="C58" s="6"/>
@@ -2119,7 +2054,7 @@
       <c r="O58" s="5"/>
       <c r="P58" s="2"/>
     </row>
-    <row r="59" spans="1:16" ht="15.6">
+    <row r="59" spans="1:16" ht="15">
       <c r="A59" s="13" t="s">
         <v>67</v>
       </c>
@@ -2143,17 +2078,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="L5:M5"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="E52:F52"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D6:E6"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="L5:M5"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2161,14 +2096,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L59"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="16.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.1328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
@@ -2199,9 +2134,7 @@
       <c r="D3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="26" t="s">
-        <v>81</v>
-      </c>
+      <c r="F3" s="26"/>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="15"/>
@@ -2254,9 +2187,7 @@
       <c r="D8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="26" t="s">
-        <v>73</v>
-      </c>
+      <c r="F8" s="26"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="15"/>
@@ -2278,9 +2209,7 @@
         <v>14</v>
       </c>
       <c r="D10" s="4"/>
-      <c r="F10" s="26" t="s">
-        <v>82</v>
-      </c>
+      <c r="F10" s="26"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="15"/>
@@ -2317,7 +2246,7 @@
       <c r="C14" s="18"/>
       <c r="D14" s="19"/>
       <c r="F14" s="26" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1">
@@ -2373,10 +2302,10 @@
       <c r="C20" s="18"/>
       <c r="D20" s="19"/>
       <c r="F20" s="26" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L20" s="26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1">
@@ -2439,7 +2368,7 @@
       </c>
       <c r="D27" s="19"/>
     </row>
-    <row r="28" spans="1:12" ht="15.6">
+    <row r="28" spans="1:12" ht="15">
       <c r="A28" s="15"/>
       <c r="B28" s="9" t="s">
         <v>18</v>
@@ -2447,7 +2376,7 @@
       <c r="C28" s="18"/>
       <c r="D28" s="19"/>
     </row>
-    <row r="29" spans="1:12" ht="15.6">
+    <row r="29" spans="1:12" ht="15">
       <c r="A29" s="15"/>
       <c r="B29" s="9" t="s">
         <v>21</v>
@@ -2455,7 +2384,7 @@
       <c r="C29" s="18"/>
       <c r="D29" s="19"/>
     </row>
-    <row r="30" spans="1:12" ht="15.6">
+    <row r="30" spans="1:12" ht="15">
       <c r="A30" s="15"/>
       <c r="B30" s="9" t="s">
         <v>23</v>
@@ -2465,7 +2394,7 @@
       </c>
       <c r="D30" s="19"/>
     </row>
-    <row r="31" spans="1:12" ht="15.6">
+    <row r="31" spans="1:12" ht="15">
       <c r="A31" s="15"/>
       <c r="B31" s="16"/>
       <c r="C31" s="10" t="s">
@@ -2473,13 +2402,13 @@
       </c>
       <c r="D31" s="19"/>
     </row>
-    <row r="32" spans="1:12" ht="15.6">
+    <row r="32" spans="1:12" ht="15">
       <c r="A32" s="15"/>
       <c r="B32" s="16"/>
       <c r="C32" s="18"/>
       <c r="D32" s="4"/>
     </row>
-    <row r="33" spans="1:7" ht="15.6">
+    <row r="33" spans="1:7" ht="15">
       <c r="A33" s="15"/>
       <c r="B33" s="23" t="s">
         <v>9</v>
@@ -2487,22 +2416,20 @@
       <c r="C33" s="18"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:7" ht="15.6">
+    <row r="34" spans="1:7" ht="15">
       <c r="A34" s="15"/>
       <c r="B34" s="16"/>
       <c r="C34" s="18"/>
       <c r="D34" s="4"/>
-      <c r="F34" s="26" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.6">
+      <c r="F34" s="26"/>
+    </row>
+    <row r="35" spans="1:7" ht="15">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="10"/>
       <c r="D35" s="4"/>
     </row>
-    <row r="36" spans="1:7" ht="15.6">
+    <row r="36" spans="1:7" ht="15">
       <c r="A36" s="8" t="s">
         <v>48</v>
       </c>
@@ -2516,7 +2443,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.6">
+    <row r="37" spans="1:7" ht="15">
       <c r="A37" s="15"/>
       <c r="B37" s="16"/>
       <c r="C37" s="10" t="s">
@@ -2524,7 +2451,7 @@
       </c>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="1:7" ht="15.6">
+    <row r="38" spans="1:7" ht="15">
       <c r="A38" s="15"/>
       <c r="B38" s="16"/>
       <c r="C38" s="10" t="s">
@@ -2532,7 +2459,7 @@
       </c>
       <c r="D38" s="22"/>
     </row>
-    <row r="39" spans="1:7" ht="15.6">
+    <row r="39" spans="1:7" ht="15">
       <c r="A39" s="15"/>
       <c r="B39" s="9" t="s">
         <v>18</v>
@@ -2542,7 +2469,7 @@
       </c>
       <c r="D39" s="4"/>
     </row>
-    <row r="40" spans="1:7" ht="15.6">
+    <row r="40" spans="1:7" ht="15">
       <c r="A40" s="15"/>
       <c r="B40" s="16"/>
       <c r="C40" s="10" t="s">
@@ -2550,18 +2477,16 @@
       </c>
       <c r="D40" s="4"/>
     </row>
-    <row r="41" spans="1:7" ht="15.6">
+    <row r="41" spans="1:7" ht="15">
       <c r="A41" s="15"/>
       <c r="B41" s="16"/>
       <c r="C41" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D41" s="4"/>
-      <c r="F41" s="25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.6">
+      <c r="F41" s="25"/>
+    </row>
+    <row r="42" spans="1:7" ht="15">
       <c r="A42" s="15"/>
       <c r="B42" s="9" t="s">
         <v>21</v>
@@ -2569,123 +2494,123 @@
       <c r="C42" s="18"/>
       <c r="D42" s="4"/>
     </row>
-    <row r="43" spans="1:7" ht="15.6">
+    <row r="43" spans="1:7" ht="15">
       <c r="A43" s="15"/>
       <c r="B43" s="16"/>
       <c r="C43" s="18"/>
       <c r="D43" s="4"/>
     </row>
-    <row r="44" spans="1:7" ht="15.6">
+    <row r="44" spans="1:7" ht="15">
       <c r="A44" s="15"/>
       <c r="B44" s="16"/>
       <c r="C44" s="18"/>
       <c r="D44" s="4"/>
     </row>
-    <row r="45" spans="1:7" ht="15.6">
+    <row r="45" spans="1:7" ht="15">
       <c r="A45" s="15"/>
       <c r="B45" s="16"/>
       <c r="C45" s="18"/>
       <c r="D45" s="4"/>
     </row>
-    <row r="46" spans="1:7" ht="15.6">
+    <row r="46" spans="1:7" ht="15">
       <c r="A46" s="15"/>
       <c r="B46" s="16"/>
       <c r="C46" s="18"/>
       <c r="D46" s="4"/>
     </row>
-    <row r="47" spans="1:7" ht="15.6">
+    <row r="47" spans="1:7" ht="15">
       <c r="A47" s="15"/>
       <c r="B47" s="16"/>
       <c r="C47" s="18"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:7" ht="15.6">
+    <row r="48" spans="1:7" ht="15">
       <c r="A48" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="18"/>
       <c r="D48" s="4"/>
       <c r="F48" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G48" s="26" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15.6">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15">
       <c r="A49" s="15"/>
       <c r="B49" s="16"/>
       <c r="C49" s="18"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:6" ht="15.6">
+    <row r="50" spans="1:6" ht="15">
       <c r="A50" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" s="16" t="s">
         <v>76</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>77</v>
       </c>
       <c r="C50" s="18"/>
       <c r="D50" s="4"/>
       <c r="F50" s="26" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15.6">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15">
       <c r="A51" s="15"/>
       <c r="B51" s="16"/>
       <c r="C51" s="18"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:6" ht="15.6">
+    <row r="52" spans="1:6" ht="15">
       <c r="A52" s="15"/>
       <c r="B52" s="16"/>
       <c r="C52" s="18"/>
       <c r="D52" s="4"/>
     </row>
-    <row r="53" spans="1:6" ht="15.6">
+    <row r="53" spans="1:6" ht="15">
       <c r="A53" s="15"/>
       <c r="B53" s="16"/>
       <c r="C53" s="18"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:6" ht="15.6">
+    <row r="54" spans="1:6" ht="15">
       <c r="A54" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="6"/>
       <c r="D54" s="4"/>
       <c r="F54" s="26" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15.6">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15">
       <c r="A55" s="5"/>
       <c r="B55" s="2"/>
       <c r="C55" s="6"/>
       <c r="D55" s="4"/>
     </row>
-    <row r="56" spans="1:6" ht="15.6">
+    <row r="56" spans="1:6" ht="15">
       <c r="A56" s="5"/>
       <c r="B56" s="2"/>
       <c r="C56" s="6"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:6" ht="15.6">
+    <row r="57" spans="1:6" ht="15">
       <c r="A57" s="5"/>
       <c r="B57" s="2"/>
       <c r="C57" s="6"/>
       <c r="D57" s="4"/>
     </row>
-    <row r="58" spans="1:6" ht="15.6">
+    <row r="58" spans="1:6" ht="15">
       <c r="A58" s="5"/>
       <c r="B58" s="2"/>
       <c r="C58" s="6"/>
       <c r="D58" s="4"/>
     </row>
-    <row r="59" spans="1:6" ht="15.6">
+    <row r="59" spans="1:6" ht="15">
       <c r="A59" s="5"/>
       <c r="B59" s="2"/>
       <c r="C59" s="6"/>
